--- a/グラフ.xlsx
+++ b/グラフ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noshi/Documents/sotsuken/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noshi\Documents\卒研\sotsuken\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43842EA5-7113-EE46-9EDC-F22DB777C5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767FF3B6-F99B-4660-96FC-397B3901D7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="760" windowWidth="28300" windowHeight="17200" activeTab="8" xr2:uid="{47A50319-132C-3D40-9578-C5D397AFB829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{47A50319-132C-3D40-9578-C5D397AFB829}"/>
   </bookViews>
   <sheets>
     <sheet name="基本条件" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <definedName name="_8" localSheetId="5">対照実験!$A$1:$B$57</definedName>
     <definedName name="pool1" localSheetId="8">プール!$A$1:$B$107</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -188,9 +188,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="192" formatCode="0.000000000000000"/>
+    <numFmt numFmtId="176" formatCode="0.000000000000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -240,7 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -982,7 +982,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -995,14 +995,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1010,8 +1010,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.4959940086023279"/>
-              <c:y val="0.93311807247115697"/>
+              <c:x val="0.49288597666550427"/>
+              <c:y val="0.91852398523985235"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1027,7 +1027,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1039,7 +1039,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1110,11 +1110,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1127,14 +1127,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1142,8 +1142,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="3.4188034188034191E-2"/>
+              <c:y val="0.43901676497079933"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1155,11 +1155,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1171,7 +1171,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1984,7 +1984,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1997,14 +1997,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2029,7 +2029,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2112,11 +2112,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2129,14 +2129,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2144,8 +2144,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="3.463855421686747E-2"/>
+              <c:y val="0.44147671651608661"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2157,11 +2157,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2986,7 +2986,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2999,14 +2999,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -3031,7 +3031,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -3113,11 +3113,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -3130,14 +3130,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -3145,8 +3145,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="4.2168674698795178E-2"/>
+              <c:y val="0.45130472634409635"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3158,11 +3158,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -3987,7 +3987,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4000,14 +4000,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -4032,7 +4032,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -4114,11 +4114,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4131,14 +4131,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -4146,8 +4146,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="3.1626506024096383E-2"/>
+              <c:y val="0.44147671651608661"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -4159,11 +4159,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -4988,7 +4988,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -5001,14 +5001,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -5016,8 +5016,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.4959940086023279"/>
-              <c:y val="0.93311807247115697"/>
+              <c:x val="0.47792168674698793"/>
+              <c:y val="0.91862407862407858"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -5033,7 +5033,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -5116,11 +5116,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -5133,14 +5133,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -5148,8 +5148,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="2.2590361445783132E-2"/>
+              <c:y val="0.45621873125810136"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -5161,11 +5161,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -5690,7 +5690,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -5703,14 +5703,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -5718,8 +5718,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.4959940086023279"/>
-              <c:y val="0.93311807247115697"/>
+              <c:x val="0.48996987951807225"/>
+              <c:y val="0.93311807154326842"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -5735,7 +5735,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -5818,11 +5818,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -5835,14 +5835,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -5850,8 +5850,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="2.710843373493976E-2"/>
+              <c:y val="0.45867573371510378"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -5863,11 +5863,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -6692,7 +6692,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -6705,14 +6705,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -6737,7 +6737,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -6820,11 +6820,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -6837,14 +6837,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -6852,8 +6852,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="2.5602409638554216E-2"/>
+              <c:y val="0.44147671651608661"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -6865,11 +6865,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -7694,7 +7694,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -7707,14 +7707,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -7739,7 +7739,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -7821,11 +7821,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -7838,14 +7838,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -7853,8 +7853,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="2.710843373493976E-2"/>
+              <c:y val="0.44147671651608661"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -7866,11 +7866,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -8695,7 +8695,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -8708,14 +8708,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>時間</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>時間  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(s)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[s]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -8740,7 +8740,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -8822,11 +8822,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -8839,14 +8839,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" sz="1400"/>
-                  <a:t>電圧</a:t>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1800"/>
+                  <a:t>電圧  </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" sz="1400"/>
-                  <a:t>(mV)</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1800"/>
+                  <a:t>[mV]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1400"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1800"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -8854,8 +8854,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0"/>
-              <c:y val="0.44147680280972074"/>
+              <c:x val="3.1626506024096383E-2"/>
+              <c:y val="0.44147671651608661"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -8867,11 +8867,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -14723,14 +14723,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F82D2D0-7A7E-8B4D-9275-0518E4739D2F}">
   <dimension ref="A1:D107"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14738,22 +14738,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -14761,7 +14761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>-0.20408001039183299</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -14785,7 +14785,7 @@
         <v>-0.20641699379255701</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -14797,7 +14797,7 @@
         <v>-0.20574928424949299</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -14809,7 +14809,7 @@
         <v>-0.20775241287868501</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>-0.20675084856408901</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -14833,7 +14833,7 @@
         <v>-0.20675084856408901</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>-0.20641699379255701</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>-0.20508157470642899</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>-0.20541542947796099</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -14881,7 +14881,7 @@
         <v>-0.20675084856408901</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>-0.20408001039183299</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>-0.20608313902102501</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>-0.20541542947796099</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -14929,7 +14929,7 @@
         <v>-0.20741855810715301</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -14941,7 +14941,7 @@
         <v>-0.20608313902102501</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>-0.20675084856408901</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>-0.20040760790498099</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -14977,7 +14977,7 @@
         <v>-0.194398222017405</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>-0.19172738384514801</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -15001,7 +15001,7 @@
         <v>-0.18638570750063599</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -15013,7 +15013,7 @@
         <v>-0.18237945024225199</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -15025,7 +15025,7 @@
         <v>-0.18204559547072</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -15037,7 +15037,7 @@
         <v>-0.178373192983868</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -15049,7 +15049,7 @@
         <v>-0.178039338212336</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -15061,7 +15061,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -15073,7 +15073,7 @@
         <v>-0.178373192983868</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -15085,7 +15085,7 @@
         <v>-0.17570235481161101</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -15097,7 +15097,7 @@
         <v>-0.179374757298464</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -15109,7 +15109,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -15121,7 +15121,7 @@
         <v>-0.179708612069996</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>-0.178373192983868</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>-0.18738727181523199</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -15169,7 +15169,7 @@
         <v>-0.18037632161306</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -15181,7 +15181,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>-0.176703919126208</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -15217,7 +15217,7 @@
         <v>-0.176703919126208</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -15229,7 +15229,7 @@
         <v>-0.177705483440804</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -15241,7 +15241,7 @@
         <v>-0.1787070477554</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -15253,7 +15253,7 @@
         <v>-0.180042466841528</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -15265,7 +15265,7 @@
         <v>-0.179040902526932</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -15277,7 +15277,7 @@
         <v>-0.179374757298464</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -15289,7 +15289,7 @@
         <v>-0.17536850004007901</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>-0.177705483440804</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -15313,7 +15313,7 @@
         <v>-0.180710176384592</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -15325,7 +15325,7 @@
         <v>-0.177705483440804</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -15337,7 +15337,7 @@
         <v>-0.17703777389774</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>-0.178039338212336</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -15361,7 +15361,7 @@
         <v>-0.17436693572548301</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -15373,7 +15373,7 @@
         <v>-0.176370064354676</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -15385,7 +15385,7 @@
         <v>-0.178039338212336</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -15397,7 +15397,7 @@
         <v>-0.1787070477554</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -15409,7 +15409,7 @@
         <v>-0.178373192983868</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -15421,7 +15421,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>-0.177705483440804</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -15445,7 +15445,7 @@
         <v>-0.176370064354676</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -15457,7 +15457,7 @@
         <v>-0.178373192983868</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>-0.18037632161306</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -15481,7 +15481,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -15493,7 +15493,7 @@
         <v>-0.1787070477554</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -15517,7 +15517,7 @@
         <v>-0.176036209583144</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -15529,7 +15529,7 @@
         <v>-0.179040902526932</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -15541,7 +15541,7 @@
         <v>-0.1787070477554</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>-0.177705483440804</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>-0.178373192983868</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -15577,7 +15577,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>-0.178039338212336</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -15601,7 +15601,7 @@
         <v>-0.179374757298464</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -15613,7 +15613,7 @@
         <v>-0.179040902526932</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -15625,7 +15625,7 @@
         <v>-0.1787070477554</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -15637,7 +15637,7 @@
         <v>-0.177371628669272</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -15649,7 +15649,7 @@
         <v>-0.176703919126208</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -15661,7 +15661,7 @@
         <v>-0.177705483440804</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>-0.179374757298464</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -15685,7 +15685,7 @@
         <v>-0.181711740699188</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>-0.17503464526854701</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>-0.18638570750063599</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -15721,7 +15721,7 @@
         <v>-0.18671956227216799</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -15733,7 +15733,7 @@
         <v>-0.19039196475902001</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -15745,7 +15745,7 @@
         <v>-0.196401350646597</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -15757,7 +15757,7 @@
         <v>-0.197402914961193</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -15769,7 +15769,7 @@
         <v>-0.199072188818853</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -15781,7 +15781,7 @@
         <v>-0.20508157470642899</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -15793,7 +15793,7 @@
         <v>-0.20441386516336499</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -15805,7 +15805,7 @@
         <v>-0.20708470333562101</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -15817,7 +15817,7 @@
         <v>-0.20975554150787701</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -15829,7 +15829,7 @@
         <v>-0.20975554150787701</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>-0.20975554150787701</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -15853,7 +15853,7 @@
         <v>-0.20708470333562101</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -15865,7 +15865,7 @@
         <v>-0.21042325105094101</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -15877,7 +15877,7 @@
         <v>-0.20875397719328101</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -15889,7 +15889,7 @@
         <v>-0.20875397719328101</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>-0.20675084856408901</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>-0.20741855810715301</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>-0.20608313902102501</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -15937,7 +15937,7 @@
         <v>-0.20741855810715301</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -15949,7 +15949,7 @@
         <v>-0.20741855810715301</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -15961,7 +15961,7 @@
         <v>-0.20842012242174901</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
@@ -15986,23 +15986,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C182B998-72F3-8044-93A2-637244EFD638}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16010,12 +16010,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -16023,7 +16023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>-114.606931621252</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -16039,7 +16039,7 @@
         <v>-112.60380299206001</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>-114.606931621252</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>-115.27464116431601</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -16063,7 +16063,7 @@
         <v>-115.27464116431601</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>-114.606931621252</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -16079,7 +16079,7 @@
         <v>-117.94547933657199</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -16087,7 +16087,7 @@
         <v>-112.26994822052801</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -16095,7 +16095,7 @@
         <v>-114.606931621252</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -16103,7 +16103,7 @@
         <v>-115.94235070738</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -16111,7 +16111,7 @@
         <v>-114.94078639278401</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>-114.94078639278401</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -16127,7 +16127,7 @@
         <v>-112.26994822052801</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -16143,7 +16143,7 @@
         <v>-110.60067436286799</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>-108.597545733676</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -16159,7 +16159,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -16167,7 +16167,7 @@
         <v>-111.60223867746399</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -16175,7 +16175,7 @@
         <v>-110.266819591336</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -16183,7 +16183,7 @@
         <v>-106.59441710448399</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>-107.92983619061199</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -16199,7 +16199,7 @@
         <v>-109.26525527673999</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -16207,7 +16207,7 @@
         <v>-106.59441710448399</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -16215,7 +16215,7 @@
         <v>-106.59441710448399</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -16223,7 +16223,7 @@
         <v>-106.59441710448399</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>-108.597545733676</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -16239,7 +16239,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -16255,7 +16255,7 @@
         <v>-109.599110048272</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -16271,7 +16271,7 @@
         <v>-108.597545733676</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -16279,7 +16279,7 @@
         <v>-110.93452913439999</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -16287,7 +16287,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -16295,7 +16295,7 @@
         <v>-110.93452913439999</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -16303,7 +16303,7 @@
         <v>-108.597545733676</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -16311,7 +16311,7 @@
         <v>-107.92983619061199</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -16319,7 +16319,7 @@
         <v>-106.59441710448399</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -16327,7 +16327,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -16343,7 +16343,7 @@
         <v>-107.59598141908</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -16351,7 +16351,7 @@
         <v>-109.599110048272</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -16359,7 +16359,7 @@
         <v>-110.60067436286799</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -16367,7 +16367,7 @@
         <v>-106.59441710448399</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -16375,7 +16375,7 @@
         <v>-111.93609344899599</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -16383,7 +16383,7 @@
         <v>-110.266819591336</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -16391,7 +16391,7 @@
         <v>-111.60223867746399</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -16399,7 +16399,7 @@
         <v>-108.597545733676</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -16407,7 +16407,7 @@
         <v>-110.60067436286799</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>-111.93609344899599</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -16439,7 +16439,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -16447,7 +16447,7 @@
         <v>-109.599110048272</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -16455,7 +16455,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -16463,7 +16463,7 @@
         <v>-107.92983619061199</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -16471,7 +16471,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -16479,7 +16479,7 @@
         <v>-108.597545733676</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -16487,7 +16487,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -16495,7 +16495,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -16503,7 +16503,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -16511,7 +16511,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>-109.599110048272</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -16527,7 +16527,7 @@
         <v>-109.26525527673999</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -16535,7 +16535,7 @@
         <v>-112.26994822052801</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -16543,7 +16543,7 @@
         <v>-109.26525527673999</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -16551,7 +16551,7 @@
         <v>-107.262126647548</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -16559,7 +16559,7 @@
         <v>-107.92983619061199</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>-107.59598141908</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -16575,7 +16575,7 @@
         <v>-107.59598141908</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -16583,7 +16583,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -16591,7 +16591,7 @@
         <v>-110.266819591336</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -16599,7 +16599,7 @@
         <v>-111.93609344899599</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -16607,7 +16607,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -16615,7 +16615,7 @@
         <v>-105.592852789888</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>-109.599110048272</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -16631,7 +16631,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -16639,7 +16639,7 @@
         <v>-108.263690962144</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -16647,7 +16647,7 @@
         <v>-110.60067436286799</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -16655,7 +16655,7 @@
         <v>-110.93452913439999</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -16663,7 +16663,7 @@
         <v>-110.266819591336</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -16671,7 +16671,7 @@
         <v>-111.60223867746399</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -16679,7 +16679,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -16687,7 +16687,7 @@
         <v>-109.599110048272</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>-108.597545733676</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -16703,7 +16703,7 @@
         <v>-109.599110048272</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -16711,7 +16711,7 @@
         <v>-110.60067436286799</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -16719,7 +16719,7 @@
         <v>-112.26994822052801</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -16727,7 +16727,7 @@
         <v>-109.932964819804</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -16735,7 +16735,7 @@
         <v>-108.931400505208</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -16743,7 +16743,7 @@
         <v>-110.93452913439999</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -16751,7 +16751,7 @@
         <v>-109.26525527673999</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -16759,7 +16759,7 @@
         <v>-111.268383905932</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>-114.94078639278401</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -16775,7 +16775,7 @@
         <v>-113.93922207818801</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -16783,7 +16783,7 @@
         <v>-113.271512535124</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -16791,7 +16791,7 @@
         <v>-112.26994822052801</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>-114.606931621252</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>-113.60536730665601</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -16815,7 +16815,7 @@
         <v>-110.60067436286799</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -16823,7 +16823,7 @@
         <v>-112.60380299206001</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
@@ -16844,23 +16844,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4631EC-6448-7043-9A4E-0EA112C44C23}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16868,12 +16868,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -16881,7 +16881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -16889,7 +16889,7 @@
         <v>27.949055822919398</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -16897,7 +16897,7 @@
         <v>27.281346279855402</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -16905,7 +16905,7 @@
         <v>26.6136367367913</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -16913,7 +16913,7 @@
         <v>23.942798564535202</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -16921,7 +16921,7 @@
         <v>26.6136367367913</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>29.952184452111499</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -16937,7 +16937,7 @@
         <v>29.2844749090475</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>28.6167653659835</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -16953,7 +16953,7 @@
         <v>26.947491508323402</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -16961,7 +16961,7 @@
         <v>30.286039223643602</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -16969,7 +16969,7 @@
         <v>27.615201051387402</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -16977,7 +16977,7 @@
         <v>28.6167653659835</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -16985,7 +16985,7 @@
         <v>28.282910594451398</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -16993,7 +16993,7 @@
         <v>28.6167653659835</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>28.6167653659835</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>30.286039223643602</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -17017,7 +17017,7 @@
         <v>30.286039223643602</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -17025,7 +17025,7 @@
         <v>29.952184452111499</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>29.2844749090475</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -17041,7 +17041,7 @@
         <v>28.6167653659835</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -17049,7 +17049,7 @@
         <v>27.615201051387402</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -17057,7 +17057,7 @@
         <v>26.2797819652593</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>26.947491508323402</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>28.6167653659835</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -17081,7 +17081,7 @@
         <v>28.9506201375155</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -17089,7 +17089,7 @@
         <v>26.6136367367913</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -17097,7 +17097,7 @@
         <v>24.944362879131301</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -17105,7 +17105,7 @@
         <v>27.281346279855402</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -17113,7 +17113,7 @@
         <v>26.2797819652593</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -17121,7 +17121,7 @@
         <v>24.944362879131301</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -17129,7 +17129,7 @@
         <v>24.610508107599202</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -17137,7 +17137,7 @@
         <v>24.944362879131301</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>27.281346279855402</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>27.281346279855402</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>23.608943793003203</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -17169,7 +17169,7 @@
         <v>23.942798564535202</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -17177,7 +17177,7 @@
         <v>21.271960392279002</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -17185,7 +17185,7 @@
         <v>21.605815163811101</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -17193,7 +17193,7 @@
         <v>24.944362879131301</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -17201,7 +17201,7 @@
         <v>24.276653336067202</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>22.6073794784071</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>24.276653336067202</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -17225,7 +17225,7 @@
         <v>24.944362879131301</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>24.276653336067202</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -17241,7 +17241,7 @@
         <v>22.273524706875101</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>20.938105620747002</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -17257,7 +17257,7 @@
         <v>19.602686534619</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -17265,7 +17265,7 @@
         <v>20.938105620747002</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -17273,7 +17273,7 @@
         <v>23.608943793003203</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>21.605815163811101</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -17289,7 +17289,7 @@
         <v>22.6073794784071</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -17297,7 +17297,7 @@
         <v>22.273524706875101</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -17305,7 +17305,7 @@
         <v>21.605815163811101</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -17313,7 +17313,7 @@
         <v>34.292296482027801</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -17321,7 +17321,7 @@
         <v>24.276653336067202</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -17329,7 +17329,7 @@
         <v>24.610508107599202</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -17337,7 +17337,7 @@
         <v>23.942798564535202</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -17345,7 +17345,7 @@
         <v>24.276653336067202</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -17353,7 +17353,7 @@
         <v>23.275089021471199</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>23.608943793003203</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>23.275089021471199</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>23.942798564535202</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -17385,7 +17385,7 @@
         <v>27.281346279855402</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -17393,7 +17393,7 @@
         <v>21.605815163811101</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -17401,7 +17401,7 @@
         <v>21.605815163811101</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>20.938105620747002</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -17417,7 +17417,7 @@
         <v>21.605815163811101</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -17425,7 +17425,7 @@
         <v>19.936541306151</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>19.936541306151</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -17441,7 +17441,7 @@
         <v>23.275089021471199</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -17449,7 +17449,7 @@
         <v>20.938105620747002</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -17457,7 +17457,7 @@
         <v>23.942798564535202</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -17465,7 +17465,7 @@
         <v>17.933412676958902</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -17473,7 +17473,7 @@
         <v>23.942798564535202</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>22.6073794784071</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -17489,7 +17489,7 @@
         <v>21.939669935343101</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>22.273524706875101</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>22.6073794784071</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -17513,7 +17513,7 @@
         <v>22.6073794784071</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>21.271960392279002</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -17529,7 +17529,7 @@
         <v>20.604250849215003</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -17537,7 +17537,7 @@
         <v>21.271960392279002</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -17545,7 +17545,7 @@
         <v>21.939669935343101</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>23.608943793003203</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -17561,7 +17561,7 @@
         <v>23.275089021471199</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -17569,7 +17569,7 @@
         <v>22.6073794784071</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>21.605815163811101</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>20.270396077682999</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -17593,7 +17593,7 @@
         <v>25.278217650663301</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>24.276653336067202</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -17609,7 +17609,7 @@
         <v>23.942798564535202</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -17617,7 +17617,7 @@
         <v>24.944362879131301</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>27.615201051387402</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -17633,7 +17633,7 @@
         <v>26.2797819652593</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -17641,7 +17641,7 @@
         <v>27.281346279855402</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -17649,7 +17649,7 @@
         <v>27.949055822919398</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -17657,7 +17657,7 @@
         <v>26.947491508323402</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>26.2797819652593</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -17673,7 +17673,7 @@
         <v>25.278217650663301</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -17681,7 +17681,7 @@
         <v>25.9459271937273</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
@@ -17702,23 +17702,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8C0DD6-5389-7E4E-BBD5-7F37633B581B}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17726,12 +17726,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -17739,7 +17739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -17747,7 +17747,7 @@
         <v>-1.4301640718981701</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -17755,7 +17755,7 @@
         <v>-1.0963093003661601</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>-1.76401884343019</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -17771,7 +17771,7 @@
         <v>-9.4744985770104095E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -17779,7 +17779,7 @@
         <v>-2.7655831580262498</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>-1.4301640718981701</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -17795,7 +17795,7 @@
         <v>0.57296455729393303</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -17803,7 +17803,7 @@
         <v>-1.4301640718981701</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>-1.76401884343019</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -17819,7 +17819,7 @@
         <v>-1.76401884343019</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -17827,7 +17827,7 @@
         <v>-0.42859975730212202</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -17835,7 +17835,7 @@
         <v>0.90681932882595206</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -17843,7 +17843,7 @@
         <v>0.57296455729393303</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -17851,7 +17851,7 @@
         <v>-0.42859975730212202</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>-1.0963093003661601</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -17867,7 +17867,7 @@
         <v>1.9083836434220001</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -17883,7 +17883,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -17891,7 +17891,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -17899,7 +17899,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -17907,7 +17907,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -17915,7 +17915,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -17923,7 +17923,7 @@
         <v>2.9099479580180598</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -17939,7 +17939,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -17947,7 +17947,7 @@
         <v>2.24223841495402</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -17955,7 +17955,7 @@
         <v>3.5776575010821001</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -17963,7 +17963,7 @@
         <v>3.5776575010821001</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -17971,7 +17971,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -17979,7 +17979,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>2.9099479580180598</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -17995,7 +17995,7 @@
         <v>2.24223841495402</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>5.2469313587421906</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -18011,7 +18011,7 @@
         <v>-9.4744985770104095E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -18019,7 +18019,7 @@
         <v>4.24536704414614</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -18027,7 +18027,7 @@
         <v>4.9130765872101696</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -18035,7 +18035,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -18043,7 +18043,7 @@
         <v>7.5839147594663201</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -18051,7 +18051,7 @@
         <v>5.2469313587421906</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -18059,7 +18059,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -18067,7 +18067,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>3.5776575010821001</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -18083,7 +18083,7 @@
         <v>4.24536704414614</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -18091,7 +18091,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -18099,7 +18099,7 @@
         <v>7.5839147594663201</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -18107,7 +18107,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -18115,7 +18115,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -18123,7 +18123,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -18131,7 +18131,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -18139,7 +18139,7 @@
         <v>5.2469313587421906</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -18147,7 +18147,7 @@
         <v>4.9130765872101696</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -18155,7 +18155,7 @@
         <v>4.24536704414614</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -18163,7 +18163,7 @@
         <v>3.5776575010821001</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -18179,7 +18179,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -18187,7 +18187,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -18195,7 +18195,7 @@
         <v>2.9099479580180598</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -18203,7 +18203,7 @@
         <v>2.9099479580180598</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -18211,7 +18211,7 @@
         <v>4.24536704414614</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>2.24223841495402</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -18227,7 +18227,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -18235,7 +18235,7 @@
         <v>0.239109785761914</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>1.24067410035797</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -18251,7 +18251,7 @@
         <v>3.5776575010821001</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -18259,7 +18259,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -18275,7 +18275,7 @@
         <v>-0.42859975730212202</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -18283,7 +18283,7 @@
         <v>-9.4744985770104095E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -18299,7 +18299,7 @@
         <v>0.239109785761914</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -18307,7 +18307,7 @@
         <v>2.9099479580180598</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -18315,7 +18315,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -18323,7 +18323,7 @@
         <v>1.24067410035797</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -18331,7 +18331,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -18339,7 +18339,7 @@
         <v>0.90681932882595206</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -18347,7 +18347,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -18355,7 +18355,7 @@
         <v>2.9099479580180598</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>2.24223841495402</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -18371,7 +18371,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -18379,7 +18379,7 @@
         <v>2.24223841495402</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -18387,7 +18387,7 @@
         <v>0.90681932882595206</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -18395,7 +18395,7 @@
         <v>0.57296455729393303</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -18403,7 +18403,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -18411,7 +18411,7 @@
         <v>1.9083836434220001</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -18419,7 +18419,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -18427,7 +18427,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -18443,7 +18443,7 @@
         <v>0.239109785761914</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -18451,7 +18451,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -18467,7 +18467,7 @@
         <v>3.24380272955008</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -18475,7 +18475,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -18483,7 +18483,7 @@
         <v>-1.0963093003661601</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>1.24067410035797</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>1.24067410035797</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>2.9099479580180598</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -18515,7 +18515,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -18523,7 +18523,7 @@
         <v>1.24067410035797</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -18531,7 +18531,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -18539,7 +18539,7 @@
         <v>3.9115122726141203</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>4.9130765872101696</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B108">
         <v>0</v>
       </c>
@@ -18565,28 +18565,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C4C8E3-320E-564F-952C-798372435DB2}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -18602,7 +18602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -18610,7 +18610,7 @@
         <v>-88.566259441755008</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>-88.232404670223005</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -18626,7 +18626,7 @@
         <v>-89.2339689848191</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -18634,7 +18634,7 @@
         <v>-89.567823756351103</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>-89.567823756351103</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -18650,7 +18650,7 @@
         <v>-86.563130812562889</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -18658,7 +18658,7 @@
         <v>-88.900114213286997</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -18674,7 +18674,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -18682,7 +18682,7 @@
         <v>-89.567823756351103</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -18690,7 +18690,7 @@
         <v>-88.232404670223005</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -18698,7 +18698,7 @@
         <v>-87.898549898691002</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -18706,7 +18706,7 @@
         <v>-87.564695127158998</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -18714,7 +18714,7 @@
         <v>-89.901678527883092</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -18722,7 +18722,7 @@
         <v>-90.235533299415096</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -18730,7 +18730,7 @@
         <v>-89.2339689848191</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>-90.235533299415096</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -18746,7 +18746,7 @@
         <v>-88.900114213286997</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -18754,7 +18754,7 @@
         <v>-91.237097614011205</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -18762,7 +18762,7 @@
         <v>-91.237097614011205</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -18770,7 +18770,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -18778,7 +18778,7 @@
         <v>-91.570952385543208</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -18786,7 +18786,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -18794,7 +18794,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -18802,7 +18802,7 @@
         <v>-93.240226243203296</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>-94.575645329331394</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -18818,7 +18818,7 @@
         <v>-94.909500100863397</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -18826,7 +18826,7 @@
         <v>-94.909500100863397</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -18834,7 +18834,7 @@
         <v>-93.574081014735299</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -18842,7 +18842,7 @@
         <v>-94.909500100863397</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -18850,7 +18850,7 @@
         <v>-93.574081014735299</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -18858,7 +18858,7 @@
         <v>-91.570952385543208</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -18866,7 +18866,7 @@
         <v>-96.24491918699151</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -18874,7 +18874,7 @@
         <v>-95.911064415459393</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>-97.580338273119509</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -18890,7 +18890,7 @@
         <v>-94.909500100863397</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -18898,7 +18898,7 @@
         <v>-95.2433548723954</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -18906,7 +18906,7 @@
         <v>-93.574081014735299</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -18914,7 +18914,7 @@
         <v>-96.912628730055502</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>-97.246483501587505</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -18930,7 +18930,7 @@
         <v>-95.577209643927389</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -18938,7 +18938,7 @@
         <v>-97.580338273119509</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -18946,7 +18946,7 @@
         <v>-96.24491918699151</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>-95.2433548723954</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -18962,7 +18962,7 @@
         <v>-95.577209643927389</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -18970,7 +18970,7 @@
         <v>-95.577209643927389</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -18978,7 +18978,7 @@
         <v>-96.24491918699151</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -18986,7 +18986,7 @@
         <v>-95.911064415459393</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -18994,7 +18994,7 @@
         <v>-94.909500100863397</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -19002,7 +19002,7 @@
         <v>-95.577209643927389</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -19010,7 +19010,7 @@
         <v>-97.246483501587505</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -19018,7 +19018,7 @@
         <v>-95.577209643927389</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>-96.24491918699151</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -19034,7 +19034,7 @@
         <v>-98.581902587715604</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>-95.2433548723954</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -19050,7 +19050,7 @@
         <v>-94.909500100863397</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -19058,7 +19058,7 @@
         <v>-95.2433548723954</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -19066,7 +19066,7 @@
         <v>-97.914193044651597</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -19074,7 +19074,7 @@
         <v>-96.24491918699151</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -19082,7 +19082,7 @@
         <v>-96.578773958523499</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -19090,7 +19090,7 @@
         <v>-97.580338273119509</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>-95.577209643927389</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -19106,7 +19106,7 @@
         <v>-96.912628730055502</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -19114,7 +19114,7 @@
         <v>-93.907935786267302</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>-92.2386619286072</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -19130,7 +19130,7 @@
         <v>-93.574081014735299</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -19138,7 +19138,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -19146,7 +19146,7 @@
         <v>-93.574081014735299</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -19154,7 +19154,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>-91.237097614011205</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>-91.237097614011205</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -19178,7 +19178,7 @@
         <v>-91.570952385543208</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -19186,7 +19186,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -19194,7 +19194,7 @@
         <v>-89.567823756351103</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -19202,7 +19202,7 @@
         <v>-89.2339689848191</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -19210,7 +19210,7 @@
         <v>-90.235533299415096</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -19218,7 +19218,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -19226,7 +19226,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -19234,7 +19234,7 @@
         <v>-90.235533299415096</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -19250,7 +19250,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -19258,7 +19258,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -19266,7 +19266,7 @@
         <v>-90.235533299415096</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -19274,7 +19274,7 @@
         <v>-90.903242842479202</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -19282,7 +19282,7 @@
         <v>-93.907935786267302</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -19290,7 +19290,7 @@
         <v>-92.906371471671306</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -19298,7 +19298,7 @@
         <v>-92.572516700139303</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -19306,7 +19306,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>-90.569388070947099</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -19322,7 +19322,7 @@
         <v>-93.240226243203296</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -19330,7 +19330,7 @@
         <v>-87.564695127158998</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>-88.566259441755008</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>-84.893856954902802</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -19354,7 +19354,7 @@
         <v>-86.2292760410309</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -19362,7 +19362,7 @@
         <v>-85.561566497966894</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -19370,7 +19370,7 @@
         <v>-85.227711726434805</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -19378,7 +19378,7 @@
         <v>-85.561566497966894</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>-85.895421269498897</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -19394,7 +19394,7 @@
         <v>-85.895421269498897</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -19402,7 +19402,7 @@
         <v>-88.900114213286997</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
@@ -19423,28 +19423,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1CB76BB-DEB0-7A47-A04F-EFCB7A8EA81D}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -19452,7 +19452,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -19460,7 +19460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -19468,7 +19468,7 @@
         <v>-162.01430917879901</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>4.9000000000000004</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>4.8</v>
       </c>
@@ -19484,7 +19484,7 @@
         <v>-164.68514735105501</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>4.7</v>
       </c>
@@ -19492,7 +19492,7 @@
         <v>-163.683583036459</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>4.5999999999999996</v>
       </c>
@@ -19500,7 +19500,7 @@
         <v>-165.35285689411899</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>4.5</v>
       </c>
@@ -19508,7 +19508,7 @@
         <v>-166.02056643718299</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>4.4000000000000004</v>
       </c>
@@ -19516,7 +19516,7 @@
         <v>-167.68984029484298</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>4.3</v>
       </c>
@@ -19524,7 +19524,7 @@
         <v>-166.354421208715</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>4.2</v>
       </c>
@@ -19532,7 +19532,7 @@
         <v>-167.68984029484298</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>4.0999999999999996</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>-164.68514735105501</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>4</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>-162.68201872186299</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>3.9</v>
       </c>
@@ -19556,7 +19556,7 @@
         <v>-165.68671166565099</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>3.8</v>
       </c>
@@ -19564,7 +19564,7 @@
         <v>-163.34972826492699</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>3.7</v>
       </c>
@@ -19572,7 +19572,7 @@
         <v>-165.01900212258698</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>3.6</v>
       </c>
@@ -19580,7 +19580,7 @@
         <v>-165.01900212258698</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>3.5</v>
       </c>
@@ -19588,7 +19588,7 @@
         <v>-162.01430917879901</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>3.4</v>
       </c>
@@ -19596,7 +19596,7 @@
         <v>-162.68201872186299</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>3.3</v>
       </c>
@@ -19604,7 +19604,7 @@
         <v>-160.34503532113899</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>3.2</v>
       </c>
@@ -19612,7 +19612,7 @@
         <v>-160.678890092671</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>3.1</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>-160.01118054960699</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>3</v>
       </c>
@@ -19628,7 +19628,7 @@
         <v>-158.341906691947</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>2.9</v>
       </c>
@@ -19636,7 +19636,7 @@
         <v>-158.67576146347901</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>2.8</v>
       </c>
@@ -19644,7 +19644,7 @@
         <v>-157.00648760581799</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>2.7</v>
       </c>
@@ -19652,7 +19652,7 @@
         <v>-160.01118054960699</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>2.6</v>
       </c>
@@ -19660,7 +19660,7 @@
         <v>-158.008051920415</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>2.5</v>
       </c>
@@ -19668,7 +19668,7 @@
         <v>-156.33877806275402</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>2.4</v>
       </c>
@@ -19676,7 +19676,7 @@
         <v>-155.67106851969001</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>2.2999999999999998</v>
       </c>
@@ -19684,7 +19684,7 @@
         <v>-153.33408511896602</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>2.2000000000000002</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>-155.003358976626</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>2.1</v>
       </c>
@@ -19700,7 +19700,7 @@
         <v>-152.66637557590201</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>2</v>
       </c>
@@ -19708,7 +19708,7 @@
         <v>-151.99866603283797</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>1.9</v>
       </c>
@@ -19716,7 +19716,7 @@
         <v>-154.00179466203002</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>1.8</v>
       </c>
@@ -19724,7 +19724,7 @@
         <v>-152.66637557590201</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>1.7</v>
       </c>
@@ -19732,7 +19732,7 @@
         <v>-152.33252080436998</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>1.6</v>
       </c>
@@ -19740,7 +19740,7 @@
         <v>-154.669504205094</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>1.5</v>
       </c>
@@ -19748,7 +19748,7 @@
         <v>-151.99866603283797</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>1.4</v>
       </c>
@@ -19756,7 +19756,7 @@
         <v>-154.00179466203002</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>1.3</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>-154.335649433562</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>1.2</v>
       </c>
@@ -19772,7 +19772,7 @@
         <v>-155.67106851969001</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>1.1000000000000001</v>
       </c>
@@ -19780,7 +19780,7 @@
         <v>-156.33877806275402</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>-156.00492329122201</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>0.9</v>
       </c>
@@ -19796,7 +19796,7 @@
         <v>-158.67576146347901</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>0.8</v>
       </c>
@@ -19804,7 +19804,7 @@
         <v>-156.33877806275402</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>0.7</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>-158.008051920415</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>0.6</v>
       </c>
@@ -19820,7 +19820,7 @@
         <v>-157.674197148882</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>0.5</v>
       </c>
@@ -19828,7 +19828,7 @@
         <v>-156.00492329122201</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>0.4</v>
       </c>
@@ -19836,7 +19836,7 @@
         <v>-155.67106851969001</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>0.3</v>
       </c>
@@ -19844,7 +19844,7 @@
         <v>-156.00492329122201</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>0.2</v>
       </c>
@@ -19852,7 +19852,7 @@
         <v>-158.008051920415</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>0.1</v>
       </c>
@@ -19860,7 +19860,7 @@
         <v>-160.01118054960699</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>0</v>
       </c>
@@ -19881,23 +19881,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77F8E26-87CA-404D-8C8F-961F1125AD9E}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -19905,12 +19905,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -19918,7 +19918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>-168.69140460943899</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -19934,7 +19934,7 @@
         <v>-168.02369506637498</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>-166.354421208715</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -19950,7 +19950,7 @@
         <v>-167.022130751779</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -19958,7 +19958,7 @@
         <v>-167.022130751779</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -19966,7 +19966,7 @@
         <v>-167.022130751779</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -19974,7 +19974,7 @@
         <v>-166.02056643718299</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -19982,7 +19982,7 @@
         <v>-164.68514735105501</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -19990,7 +19990,7 @@
         <v>-165.35285689411899</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>-165.68671166565099</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -20006,7 +20006,7 @@
         <v>-166.354421208715</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -20014,7 +20014,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -20022,7 +20022,7 @@
         <v>-164.68514735105501</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -20030,7 +20030,7 @@
         <v>-165.01900212258698</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -20038,7 +20038,7 @@
         <v>-164.68514735105501</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -20046,7 +20046,7 @@
         <v>-165.01900212258698</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -20054,7 +20054,7 @@
         <v>-166.688275980247</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -20062,7 +20062,7 @@
         <v>-164.351292579523</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -20070,7 +20070,7 @@
         <v>-165.35285689411899</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -20078,7 +20078,7 @@
         <v>-165.35285689411899</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -20086,7 +20086,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -20094,7 +20094,7 @@
         <v>-164.017437807991</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>-164.68514735105501</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -20110,7 +20110,7 @@
         <v>-164.351292579523</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -20118,7 +20118,7 @@
         <v>-163.683583036459</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -20126,7 +20126,7 @@
         <v>-161.012744864203</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>-164.351292579523</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>-164.68514735105501</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -20150,7 +20150,7 @@
         <v>-164.351292579523</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -20158,7 +20158,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -20166,7 +20166,7 @@
         <v>-163.34972826492699</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -20174,7 +20174,7 @@
         <v>-163.34972826492699</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -20182,7 +20182,7 @@
         <v>-164.351292579523</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -20190,7 +20190,7 @@
         <v>-164.351292579523</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -20198,7 +20198,7 @@
         <v>-162.34816395033099</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -20206,7 +20206,7 @@
         <v>-163.683583036459</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -20214,7 +20214,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -20222,7 +20222,7 @@
         <v>-160.678890092671</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -20230,7 +20230,7 @@
         <v>-162.68201872186299</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -20238,7 +20238,7 @@
         <v>-162.68201872186299</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -20246,7 +20246,7 @@
         <v>-163.683583036459</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -20254,7 +20254,7 @@
         <v>-163.34972826492699</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -20262,7 +20262,7 @@
         <v>-163.34972826492699</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -20270,7 +20270,7 @@
         <v>-160.678890092671</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -20278,7 +20278,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -20286,7 +20286,7 @@
         <v>-161.346599635735</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -20294,7 +20294,7 @@
         <v>-161.346599635735</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -20310,7 +20310,7 @@
         <v>-160.678890092671</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>-161.012744864203</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -20326,7 +20326,7 @@
         <v>-167.68984029484298</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>-162.01430917879901</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -20342,7 +20342,7 @@
         <v>-170.69453323863101</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -20350,7 +20350,7 @@
         <v>-161.68045440726701</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>-161.68045440726701</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -20366,7 +20366,7 @@
         <v>-162.68201872186299</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -20374,7 +20374,7 @@
         <v>-160.01118054960699</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -20382,7 +20382,7 @@
         <v>-159.67732577807502</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -20390,7 +20390,7 @@
         <v>-162.34816395033099</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -20398,7 +20398,7 @@
         <v>-162.34816395033099</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -20406,7 +20406,7 @@
         <v>-163.683583036459</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -20414,7 +20414,7 @@
         <v>-163.01587349339499</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -20422,7 +20422,7 @@
         <v>-161.346599635735</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>-161.346599635735</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -20438,7 +20438,7 @@
         <v>-161.012744864203</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -20446,7 +20446,7 @@
         <v>-161.012744864203</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -20454,7 +20454,7 @@
         <v>-161.68045440726701</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -20462,7 +20462,7 @@
         <v>-158.341906691947</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -20470,7 +20470,7 @@
         <v>-160.34503532113899</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -20478,7 +20478,7 @@
         <v>-161.346599635735</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -20486,7 +20486,7 @@
         <v>-161.012744864203</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -20494,7 +20494,7 @@
         <v>-161.68045440726701</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -20502,7 +20502,7 @@
         <v>-162.34816395033099</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -20510,7 +20510,7 @@
         <v>-162.68201872186299</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -20518,7 +20518,7 @@
         <v>-162.01430917879901</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -20526,7 +20526,7 @@
         <v>-163.683583036459</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -20534,7 +20534,7 @@
         <v>-163.683583036459</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>-165.35285689411899</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -20550,7 +20550,7 @@
         <v>-164.017437807991</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -20558,7 +20558,7 @@
         <v>-166.02056643718299</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -20566,7 +20566,7 @@
         <v>-167.68984029484298</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -20574,7 +20574,7 @@
         <v>-168.69140460943899</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -20582,7 +20582,7 @@
         <v>-169.02525938097099</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -20590,7 +20590,7 @@
         <v>-167.35598552331098</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -20598,7 +20598,7 @@
         <v>-167.35598552331098</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -20606,7 +20606,7 @@
         <v>-167.35598552331098</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -20614,7 +20614,7 @@
         <v>-167.68984029484298</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -20622,7 +20622,7 @@
         <v>-168.02369506637498</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -20630,7 +20630,7 @@
         <v>-168.69140460943899</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -20638,7 +20638,7 @@
         <v>-167.35598552331098</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>-169.02525938097099</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -20654,7 +20654,7 @@
         <v>-167.68984029484298</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -20662,7 +20662,7 @@
         <v>-167.022130751779</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -20670,7 +20670,7 @@
         <v>-169.359114152503</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -20678,7 +20678,7 @@
         <v>-167.022130751779</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -20686,7 +20686,7 @@
         <v>-168.69140460943899</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>-168.35754983790699</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -20702,7 +20702,7 @@
         <v>-167.68984029484298</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -20710,7 +20710,7 @@
         <v>-169.692968924035</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -20718,7 +20718,7 @@
         <v>-171.36224278169502</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
@@ -20739,23 +20739,23 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF8C0F2-03C2-7540-A4E4-91CD8057777F}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -20763,12 +20763,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -20776,7 +20776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -20784,7 +20784,7 @@
         <v>64.673080691441498</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -20792,7 +20792,7 @@
         <v>64.673080691441498</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>64.005371148377492</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -20808,7 +20808,7 @@
         <v>64.005371148377492</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -20816,7 +20816,7 @@
         <v>64.005371148377492</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -20824,7 +20824,7 @@
         <v>61.334532976121302</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -20832,7 +20832,7 @@
         <v>60.666823433057303</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -20840,7 +20840,7 @@
         <v>61.334532976121302</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -20848,7 +20848,7 @@
         <v>64.339225919909495</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -20856,7 +20856,7 @@
         <v>59.665259118461201</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -20864,7 +20864,7 @@
         <v>64.339225919909495</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -20872,7 +20872,7 @@
         <v>61.334532976121302</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -20880,7 +20880,7 @@
         <v>63.671516376845396</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>62.002242519185295</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -20896,7 +20896,7 @@
         <v>61.668387747653298</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>59.665259118461201</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -20912,7 +20912,7 @@
         <v>59.331404346929197</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -20920,7 +20920,7 @@
         <v>58.663694803865098</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>55.659001860077005</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -20936,7 +20936,7 @@
         <v>54.991292317012899</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -20944,7 +20944,7 @@
         <v>53.322018459352797</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -20952,7 +20952,7 @@
         <v>52.654308916288798</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -20960,7 +20960,7 @@
         <v>55.659001860077005</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -20968,7 +20968,7 @@
         <v>50.317325515564697</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -20976,7 +20976,7 @@
         <v>50.985035058628696</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -20984,7 +20984,7 @@
         <v>51.986599373224799</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -20992,7 +20992,7 @@
         <v>52.654308916288798</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>51.3188898301607</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -21008,7 +21008,7 @@
         <v>50.317325515564697</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -21016,7 +21016,7 @@
         <v>50.6511802870967</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>49.315761200968602</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -21032,7 +21032,7 @@
         <v>50.317325515564697</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -21040,7 +21040,7 @@
         <v>49.983470744032701</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -21048,7 +21048,7 @@
         <v>51.3188898301607</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -21056,7 +21056,7 @@
         <v>51.3188898301607</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -21064,7 +21064,7 @@
         <v>52.988163687820801</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>51.986599373224799</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -21080,7 +21080,7 @@
         <v>48.981906429436606</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -21088,7 +21088,7 @@
         <v>51.986599373224799</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -21096,7 +21096,7 @@
         <v>49.315761200968602</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -21104,7 +21104,7 @@
         <v>48.981906429436606</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -21112,7 +21112,7 @@
         <v>51.3188898301607</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -21120,7 +21120,7 @@
         <v>49.983470744032701</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -21128,7 +21128,7 @@
         <v>49.315761200968602</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -21136,7 +21136,7 @@
         <v>51.986599373224799</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>47.6464873433085</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -21152,7 +21152,7 @@
         <v>49.315761200968602</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -21160,7 +21160,7 @@
         <v>47.980342114840596</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -21168,7 +21168,7 @@
         <v>48.314196886372599</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -21176,7 +21176,7 @@
         <v>49.315761200968602</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -21184,7 +21184,7 @@
         <v>48.648051657904595</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -21192,7 +21192,7 @@
         <v>49.649615972500605</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -21200,7 +21200,7 @@
         <v>48.648051657904595</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -21208,7 +21208,7 @@
         <v>47.312632571776504</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>47.980342114840596</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -21224,7 +21224,7 @@
         <v>45.309503942584399</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -21232,7 +21232,7 @@
         <v>46.978777800244501</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -21240,7 +21240,7 @@
         <v>46.311068257180501</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -21248,7 +21248,7 @@
         <v>45.643358714116403</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -21256,7 +21256,7 @@
         <v>45.309503942584399</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -21264,7 +21264,7 @@
         <v>48.314196886372599</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -21272,7 +21272,7 @@
         <v>53.322018459352797</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -21280,7 +21280,7 @@
         <v>53.322018459352797</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>52.654308916288798</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -21296,7 +21296,7 @@
         <v>47.312632571776504</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>46.978777800244501</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -21312,7 +21312,7 @@
         <v>52.320454144756802</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -21320,7 +21320,7 @@
         <v>47.980342114840596</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -21328,7 +21328,7 @@
         <v>51.3188898301607</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -21336,7 +21336,7 @@
         <v>58.329840032333102</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -21344,7 +21344,7 @@
         <v>58.663694803865098</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -21352,7 +21352,7 @@
         <v>57.3282757177371</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>55.325147088545002</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -21368,7 +21368,7 @@
         <v>58.329840032333102</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -21376,7 +21376,7 @@
         <v>58.997549575397201</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -21384,7 +21384,7 @@
         <v>58.329840032333102</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -21392,7 +21392,7 @@
         <v>59.331404346929197</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -21400,7 +21400,7 @@
         <v>60.3329686615252</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -21408,7 +21408,7 @@
         <v>64.005371148377492</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -21416,7 +21416,7 @@
         <v>60.666823433057303</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -21424,7 +21424,7 @@
         <v>58.663694803865098</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>60.3329686615252</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -21440,7 +21440,7 @@
         <v>59.999113889993197</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -21448,7 +21448,7 @@
         <v>62.669952062249401</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -21456,7 +21456,7 @@
         <v>61.334532976121302</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -21464,7 +21464,7 @@
         <v>60.3329686615252</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -21472,7 +21472,7 @@
         <v>60.666823433057303</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -21480,7 +21480,7 @@
         <v>60.3329686615252</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -21488,7 +21488,7 @@
         <v>59.665259118461201</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -21496,7 +21496,7 @@
         <v>62.669952062249401</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -21504,7 +21504,7 @@
         <v>55.992856631609001</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -21512,7 +21512,7 @@
         <v>57.662130489269103</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -21520,7 +21520,7 @@
         <v>57.995985260801106</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>57.3282757177371</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -21536,7 +21536,7 @@
         <v>58.997549575397201</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -21544,7 +21544,7 @@
         <v>60.3329686615252</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -21552,7 +21552,7 @@
         <v>55.992856631609001</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>68.011628406761702</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -21568,7 +21568,7 @@
         <v>57.995985260801106</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -21576,7 +21576,7 @@
         <v>57.3282757177371</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
@@ -21597,28 +21597,28 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D3F4B8-B18F-A54A-A196-E8A6C648343F}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -21634,7 +21634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>14.594864961638701</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.9</v>
       </c>
@@ -21650,7 +21650,7 @@
         <v>17.599557905426803</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9.8000000000000007</v>
       </c>
@@ -21658,7 +21658,7 @@
         <v>17.933412676958902</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9.6999999999999993</v>
       </c>
@@ -21666,7 +21666,7 @@
         <v>19.602686534619</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9.6</v>
       </c>
@@ -21674,7 +21674,7 @@
         <v>27.949055822919398</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9.5</v>
       </c>
@@ -21682,7 +21682,7 @@
         <v>20.270396077682999</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>9.4</v>
       </c>
@@ -21690,7 +21690,7 @@
         <v>17.933412676958902</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>9.3000000000000007</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>12.2578815609145</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>9.1999999999999993</v>
       </c>
@@ -21706,7 +21706,7 @@
         <v>-0.42859975730212202</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>9.1</v>
       </c>
@@ -21714,7 +21714,7 @@
         <v>20.938105620747002</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>9</v>
       </c>
@@ -21722,7 +21722,7 @@
         <v>16.5979935908308</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8.9</v>
       </c>
@@ -21730,7 +21730,7 @@
         <v>18.934976991554901</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8.8000000000000007</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>25.9459271937273</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>8.6999999999999993</v>
       </c>
@@ -21746,7 +21746,7 @@
         <v>21.939669935343101</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>8.6</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>12.2578815609145</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>8.5</v>
       </c>
@@ -21762,7 +21762,7 @@
         <v>9.2531886171264208</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>8.4</v>
       </c>
@@ -21770,7 +21770,7 @@
         <v>-7.1056951879424899</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>8.3000000000000007</v>
       </c>
@@ -21778,7 +21778,7 @@
         <v>14.261010190106701</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>8.1999999999999993</v>
       </c>
@@ -21786,7 +21786,7 @@
         <v>16.2641388192988</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>8.1</v>
       </c>
@@ -21794,7 +21794,7 @@
         <v>18.267267448490902</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>8</v>
       </c>
@@ -21802,7 +21802,7 @@
         <v>5.2469313587421906</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>7.9</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>11.256317246318501</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>7.8</v>
       </c>
@@ -21818,7 +21818,7 @@
         <v>12.591736332446601</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>7.7</v>
       </c>
@@ -21826,7 +21826,7 @@
         <v>11.590172017850501</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>7.6</v>
       </c>
@@ -21834,7 +21834,7 @@
         <v>20.270396077682999</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>7.5</v>
       </c>
@@ -21842,7 +21842,7 @@
         <v>19.602686534619</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>7.4</v>
       </c>
@@ -21850,7 +21850,7 @@
         <v>16.2641388192988</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>7.3</v>
       </c>
@@ -21858,7 +21858,7 @@
         <v>8.2516243025303595</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>7.2</v>
       </c>
@@ -21866,7 +21866,7 @@
         <v>23.608943793003203</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>7.1</v>
       </c>
@@ -21874,7 +21874,7 @@
         <v>17.933412676958902</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>7</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>16.9318483623628</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>6.9</v>
       </c>
@@ -21890,7 +21890,7 @@
         <v>15.2625745047027</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>6.8</v>
       </c>
@@ -21898,7 +21898,7 @@
         <v>13.2594458755106</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>6.7</v>
       </c>
@@ -21906,7 +21906,7 @@
         <v>12.2578815609145</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>6.6</v>
       </c>
@@ -21914,7 +21914,7 @@
         <v>14.261010190106701</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>6.5</v>
       </c>
@@ -21922,7 +21922,7 @@
         <v>22.273524706875101</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>6.4</v>
       </c>
@@ -21930,7 +21930,7 @@
         <v>8.9193338455943998</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>6.3</v>
       </c>
@@ -21938,7 +21938,7 @@
         <v>16.2641388192988</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>6.2</v>
       </c>
@@ -21946,7 +21946,7 @@
         <v>17.265703133894799</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>20.938105620747002</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>6</v>
       </c>
@@ -21962,7 +21962,7 @@
         <v>6.2484956733382502</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>5.2469313587421906</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>5.8</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>12.591736332446601</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>5.7</v>
       </c>
@@ -21986,7 +21986,7 @@
         <v>-1.76401884343019</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>5.6</v>
       </c>
@@ -21994,7 +21994,7 @@
         <v>0.57296455729393303</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>5.5</v>
       </c>
@@ -22002,7 +22002,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>5.4</v>
       </c>
@@ -22010,7 +22010,7 @@
         <v>-2.0978736149622104</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>5.3</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>5.91464090180623</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>5.2</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>-8.1072595025385485</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>5.0999999999999996</v>
       </c>
@@ -22034,7 +22034,7 @@
         <v>-7.7734047310065302</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>5</v>
       </c>
@@ -22042,7 +22042,7 @@
         <v>-0.42859975730212202</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>4.9000000000000004</v>
       </c>
@@ -22050,7 +22050,7 @@
         <v>-11.111952446326699</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>4.8</v>
       </c>
@@ -22058,7 +22058,7 @@
         <v>-7.43954995947451</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>4.7</v>
       </c>
@@ -22066,7 +22066,7 @@
         <v>-11.7796619893907</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>4.5999999999999996</v>
       </c>
@@ -22074,7 +22074,7 @@
         <v>-8.7749690456025906</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>4.5</v>
       </c>
@@ -22082,7 +22082,7 @@
         <v>-2.4317283864942301</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>4.4000000000000004</v>
       </c>
@@ -22090,7 +22090,7 @@
         <v>-5.4364213302823998</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>4.3</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>-1.0963093003661601</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>4.2</v>
       </c>
@@ -22106,7 +22106,7 @@
         <v>-6.4379856448784603</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>4.0999999999999996</v>
       </c>
@@ -22114,7 +22114,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>-5.4364213302823998</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>3.9</v>
       </c>
@@ -22130,7 +22130,7 @@
         <v>-13.4489358470508</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>3.8</v>
       </c>
@@ -22138,7 +22138,7 @@
         <v>-20.7937408207552</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>3.7</v>
       </c>
@@ -22146,7 +22146,7 @@
         <v>-16.453628790839002</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>3.6</v>
       </c>
@@ -22154,7 +22154,7 @@
         <v>-16.119774019307002</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>3.5</v>
       </c>
@@ -22162,7 +22162,7 @@
         <v>-4.7687117872183604</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>3.4</v>
       </c>
@@ -22170,7 +22170,7 @@
         <v>-4.1010022441543201</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>3.3</v>
       </c>
@@ -22178,7 +22178,7 @@
         <v>-3.4332927010902901</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>3.2</v>
       </c>
@@ -22186,7 +22186,7 @@
         <v>5.5807861302742099</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>3.1</v>
       </c>
@@ -22194,7 +22194,7 @@
         <v>8.5854790740623788</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>3</v>
       </c>
@@ -22202,7 +22202,7 @@
         <v>10.5886077032545</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2.9</v>
       </c>
@@ -22210,7 +22210,7 @@
         <v>-0.42859975730212202</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2.8</v>
       </c>
@@ -22218,7 +22218,7 @@
         <v>7.9177695309983402</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2.7</v>
       </c>
@@ -22226,7 +22226,7 @@
         <v>3.5776575010821001</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>2.6</v>
       </c>
@@ -22234,7 +22234,7 @@
         <v>6.5823504448702694</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2.5</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>4.5792218156781495</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2.4</v>
       </c>
@@ -22250,7 +22250,7 @@
         <v>5.91464090180623</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2.2999999999999998</v>
       </c>
@@ -22258,7 +22258,7 @@
         <v>5.91464090180623</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2.2000000000000002</v>
       </c>
@@ -22266,7 +22266,7 @@
         <v>7.9177695309983402</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2.1</v>
       </c>
@@ -22274,7 +22274,7 @@
         <v>7.2500599879343</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -22282,7 +22282,7 @@
         <v>2.5760931864860401</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>1.9</v>
       </c>
@@ -22290,7 +22290,7 @@
         <v>1.9083836434220001</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>1.8</v>
       </c>
@@ -22298,7 +22298,7 @@
         <v>0.90681932882595206</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>1.7</v>
       </c>
@@ -22306,7 +22306,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>1.6</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>-2.4317283864942301</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>1.5</v>
       </c>
@@ -22322,7 +22322,7 @@
         <v>-3.0994379295582699</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>1.4</v>
       </c>
@@ -22330,7 +22330,7 @@
         <v>-3.4332927010902901</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>1.3</v>
       </c>
@@ -22338,7 +22338,7 @@
         <v>-1.0963093003661601</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>1.2</v>
       </c>
@@ -22346,7 +22346,7 @@
         <v>-5.4364213302823998</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>1.1000000000000001</v>
       </c>
@@ -22354,7 +22354,7 @@
         <v>-3.7671474726223102</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>1</v>
       </c>
@@ -22362,7 +22362,7 @@
         <v>-7.7734047310065302</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.9</v>
       </c>
@@ -22370,7 +22370,7 @@
         <v>-2.4317283864942301</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.8</v>
       </c>
@@ -22378,7 +22378,7 @@
         <v>-1.76401884343019</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.7</v>
       </c>
@@ -22386,7 +22386,7 @@
         <v>-2.7655831580262498</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.6</v>
       </c>
@@ -22394,7 +22394,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.5</v>
       </c>
@@ -22402,7 +22402,7 @@
         <v>0.239109785761914</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.4</v>
       </c>
@@ -22410,7 +22410,7 @@
         <v>1.24067410035797</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.3</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>1.5745288718899901</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.2</v>
       </c>
@@ -22426,7 +22426,7 @@
         <v>-4.7687117872183604</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.1</v>
       </c>
@@ -22434,7 +22434,7 @@
         <v>2.24223841495402</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0</v>
       </c>
